--- a/artfynd/A 12640-2024 artfynd.xlsx
+++ b/artfynd/A 12640-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103998024</v>
+        <v>103998080</v>
       </c>
       <c r="B2" t="n">
-        <v>90634</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>564973.8103650901</v>
+        <v>564811</v>
       </c>
       <c r="R2" t="n">
-        <v>7005862.236279798</v>
+        <v>7006021</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>07:59</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,16 +794,11 @@
         <v>103998154</v>
       </c>
       <c r="B3" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -836,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>564792.1714213241</v>
+        <v>564792</v>
       </c>
       <c r="R3" t="n">
-        <v>7006076.787586674</v>
+        <v>7006077</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -917,37 +907,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>103998080</v>
+        <v>103998024</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>564810.929361414</v>
+        <v>564974</v>
       </c>
       <c r="R4" t="n">
-        <v>7006021.147432731</v>
+        <v>7005862</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1002,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>07:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,12 +1026,7 @@
         <v>103998062</v>
       </c>
       <c r="B5" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>564956.5975829236</v>
+        <v>564956</v>
       </c>
       <c r="R5" t="n">
-        <v>7005885.834066432</v>
+        <v>7005886</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1152,6 +1132,122 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>103998042</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>564877</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7005903</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-08-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-08-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>

--- a/artfynd/A 12640-2024 artfynd.xlsx
+++ b/artfynd/A 12640-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998080</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998154</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998024</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998062</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,8 +1277,20 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103998042</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>